--- a/output_data/charts/1600000US3905130.xlsx
+++ b/output_data/charts/1600000US3905130.xlsx
@@ -207,7 +207,7 @@
                   <c:v>13656</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14109</c:v>
+                  <c:v>14112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -250,7 +250,7 @@
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="15534.2"/>
+          <c:max val="15532.000000000002"/>
           <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -672,7 +672,7 @@
         <v>44013</v>
       </c>
       <c r="B6" s="2">
-        <v>14109</v>
+        <v>14112</v>
       </c>
     </row>
   </sheetData>
